--- a/entrepreneur_forms/014_virtual_assistant_survey--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/014_virtual_assistant_survey--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>business_location_1</t>
+          <t>business location 1</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>business_location_2</t>
+          <t>business location 2</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>business_location_3</t>
+          <t>business location 3</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>business_location_4</t>
+          <t>business location 4</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>business_location_5</t>
+          <t>business location 5</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>business_location_6</t>
+          <t>business location 6</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_method_1</t>
+          <t>contact method 1</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_method_2</t>
+          <t>contact method 2</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_method_3</t>
+          <t>contact method 3</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_method_4</t>
+          <t>contact method 4</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_method_5</t>
+          <t>contact method 5</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>availability_status_1</t>
+          <t>availability status 1</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>availability_status_2</t>
+          <t>availability status 2</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>availability_status_3</t>
+          <t>availability status 3</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>availability_status_4</t>
+          <t>availability status 4</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>availability_status_5</t>
+          <t>availability status 5</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>work_status_1</t>
+          <t>work status 1</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>work_status_2</t>
+          <t>work status 2</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>work_status_3</t>
+          <t>work status 3</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>work_status_4</t>
+          <t>work status 4</t>
         </is>
       </c>
     </row>
